--- a/JUGADORES T7.xlsx
+++ b/JUGADORES T7.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bots\pp_consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E0F1F856-331B-4A23-941B-2F5B0C3BB618}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6176B45-A1A5-49A9-9A8D-05958BA25C0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{A98060DC-1932-43E6-9169-0378406E7D7E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A98060DC-1932-43E6-9169-0378406E7D7E}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
   <si>
     <t>Rubén Serna</t>
   </si>
@@ -105,9 +105,6 @@
     <t>Jorge Alberola</t>
   </si>
   <si>
-    <t>Álvaro Monleon</t>
-  </si>
-  <si>
     <t>Alex Navarro</t>
   </si>
   <si>
@@ -132,9 +129,6 @@
     <t>Abigail Christie</t>
   </si>
   <si>
-    <t>Jorge Stuyck</t>
-  </si>
-  <si>
     <t>Leonardo Muñoz</t>
   </si>
   <si>
@@ -154,6 +148,24 @@
   </si>
   <si>
     <t>Borja Carmona</t>
+  </si>
+  <si>
+    <t>Álvaro Monleón</t>
+  </si>
+  <si>
+    <t>Jesús Sancho</t>
+  </si>
+  <si>
+    <t>Pablo Bellido</t>
+  </si>
+  <si>
+    <t>Rafael Tortolero</t>
+  </si>
+  <si>
+    <t>Domingo Perales</t>
+  </si>
+  <si>
+    <t>Alejandro León</t>
   </si>
 </sst>
 </file>
@@ -169,12 +181,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -189,8 +207,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -505,7 +524,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA3AEB69-7505-4905-87B6-66EA901D9D74}">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.5546875" bestFit="1" customWidth="1"/>
@@ -517,149 +536,163 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="D1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="E1" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="E2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E3" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="D4" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E4" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="E5" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="D6" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E6" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="D7" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>7</v>
+      <c r="A8" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="D8" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="E8" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>25</v>
+      </c>
+      <c r="B9" t="s">
+        <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="D9" t="s">
-        <v>34</v>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/JUGADORES T7.xlsx
+++ b/JUGADORES T7.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bots\pp_consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6176B45-A1A5-49A9-9A8D-05958BA25C0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D141D8FD-D05D-48BE-B6A8-8A6D3DD6B7D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A98060DC-1932-43E6-9169-0378406E7D7E}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{A98060DC-1932-43E6-9169-0378406E7D7E}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -528,10 +528,10 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">

--- a/JUGADORES T7.xlsx
+++ b/JUGADORES T7.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bots\pp_consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D141D8FD-D05D-48BE-B6A8-8A6D3DD6B7D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04F2F444-EA18-42C3-BE60-3590CF832068}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{A98060DC-1932-43E6-9169-0378406E7D7E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>Rubén Serna</t>
   </si>
@@ -151,9 +151,6 @@
   </si>
   <si>
     <t>Álvaro Monleón</t>
-  </si>
-  <si>
-    <t>Jesús Sancho</t>
   </si>
   <si>
     <t>Pablo Bellido</t>
@@ -181,18 +178,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -209,7 +200,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -644,13 +635,13 @@
         <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="D7" t="s">
         <v>38</v>
       </c>
       <c r="E7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -661,13 +652,13 @@
         <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="D8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -678,10 +669,10 @@
         <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="D9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -690,9 +681,6 @@
       </c>
       <c r="B10" t="s">
         <v>8</v>
-      </c>
-      <c r="C10" t="s">
-        <v>29</v>
       </c>
     </row>
   </sheetData>
